--- a/output/full_scan/batch_seq8_2026-09-02.xlsx
+++ b/output/full_scan/batch_seq8_2026-09-02.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O128"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -633,21 +633,21 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6870</v>
+        <v>6933</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>776.6983472806833</v>
+        <v>852.5116825476343</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.88254633017743</v>
+        <v>87.93190943502962</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>11.32218828050776</v>
+        <v>35.82925279899008</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.90394032099514</v>
+        <v>1.351168254763432</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>3.171671565418405</v>
+        <v>13.91075380843786</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6859</v>
+        <v>6870</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>768.4913747749243</v>
+        <v>776.6983472806833</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>113.5</v>
+        <v>292</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>59.89263394669771</v>
+        <v>64.88254633017743</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>22.5389332724763</v>
+        <v>11.32218828050776</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.009531455005217</v>
+        <v>3.90394032099514</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.8171667671030769</v>
+        <v>3.171671565418405</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7711</v>
+        <v>6859</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>768.0427000820107</v>
+        <v>768.4913747749243</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>610</v>
+        <v>113.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>79.36451040152238</v>
+        <v>59.89263394669771</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>47.05093068430579</v>
+        <v>22.5389332724763</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.507760443296379</v>
+        <v>2.009531455005217</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>9.127930794473102</v>
+        <v>0.8171667671030769</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6840</v>
+        <v>7711</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>735.8148487565126</v>
+        <v>768.0427000820107</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>92.3</v>
+        <v>610</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>71.55211775938591</v>
+        <v>79.36451040152238</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>39.69914937459316</v>
+        <v>47.05093068430579</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.8432020110943278</v>
+        <v>1.507760443296379</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.8606041537507965</v>
+        <v>9.127930794473102</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6907</v>
+        <v>6840</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>726.4082719542562</v>
+        <v>735.8148487565126</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>191</v>
+        <v>92.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>54.18289216963569</v>
+        <v>71.55211775938591</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15.91629633166287</v>
+        <v>39.69914937459316</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.512102044919886</v>
+        <v>0.8432020110943278</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>3</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1887807720131675</v>
+        <v>0.8606041537507965</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7738</v>
+        <v>6907</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>726.0304712144978</v>
+        <v>726.4082719542562</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.73185262302476</v>
+        <v>54.18289216963569</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>32.68330303990491</v>
+        <v>15.91629633166287</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.199663206500234</v>
+        <v>0.512102044919886</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.3584167173083837</v>
+        <v>0.1887807720131675</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7556</v>
+        <v>7738</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>721.2907852467695</v>
+        <v>726.0304712144978</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>252.5</v>
+        <v>171</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>56.25275058264937</v>
+        <v>56.73185262302476</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>28.44427586514069</v>
+        <v>32.68330303990491</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.5926414069259714</v>
+        <v>1.199663206500234</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.487359496139391</v>
+        <v>0.3584167173083837</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>7728</v>
+        <v>7556</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>716.7233694540994</v>
+        <v>721.2907852467695</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>667</v>
+        <v>252.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>64.29415876580265</v>
+        <v>56.25275058264937</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>22.54325551189722</v>
+        <v>28.44427586514069</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.772336945409937</v>
+        <v>0.5926414069259714</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>10.64814171302243</v>
+        <v>1.487359496139391</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6854</v>
+        <v>7728</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>697.4507448523159</v>
+        <v>716.7233694540994</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>99.5</v>
+        <v>667</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>56.53542424677188</v>
+        <v>64.29415876580265</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>23.29656430963114</v>
+        <v>22.54325551189722</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.324961078743184</v>
+        <v>2.772336945409937</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.564289052944802</v>
+        <v>10.64814171302243</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6885</v>
+        <v>6854</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>685.0705115064692</v>
+        <v>697.4507448523159</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>24.6</v>
+        <v>99.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>77.59560471141477</v>
+        <v>56.53542424677188</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>32.70011416029893</v>
+        <v>23.29656430963114</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.858205546912996</v>
+        <v>3.324961078743184</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.4079138839783226</v>
+        <v>1.564289052944802</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6922</v>
+        <v>6885</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>665.7224804568003</v>
+        <v>685.0705115064692</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>206.5</v>
+        <v>24.6</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>57.29956130113769</v>
+        <v>77.59560471141477</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>27.51435825255285</v>
+        <v>32.70011416029893</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.3067183020716313</v>
+        <v>2.858205546912996</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.08052301103719189</v>
+        <v>0.4079138839783226</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6937</v>
+        <v>6922</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>629.303511941792</v>
+        <v>665.7224804568003</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>293.5</v>
+        <v>206.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>59.05962184749696</v>
+        <v>57.29956130113769</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>11.72323390616761</v>
+        <v>27.51435825255285</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3.730351194179198</v>
+        <v>0.3067183020716313</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2.570760193911862</v>
+        <v>-0.08052301103719189</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6913</v>
+        <v>6937</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>615.1691516676752</v>
+        <v>629.303511941792</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>153</v>
+        <v>293.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>58.66560524286117</v>
+        <v>59.05962184749696</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>29.24492834836501</v>
+        <v>11.72323390616761</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.8543731144622251</v>
+        <v>3.730351194179198</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.084572265298114</v>
+        <v>2.570760193911862</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6894</v>
+        <v>6913</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>612.3893071729051</v>
+        <v>615.1691516676752</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>356</v>
+        <v>153</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>60.49688003750874</v>
+        <v>58.66560524286117</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>14.73889817310458</v>
+        <v>29.24492834836501</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.038930717290511</v>
+        <v>0.8543731144622251</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>1</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>3.20194330264459</v>
+        <v>1.084572265298114</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7792</v>
+        <v>6894</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>607.5373069701751</v>
+        <v>612.3893071729051</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>308</v>
+        <v>356</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>70.72581604299671</v>
+        <v>60.49688003750874</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>49.69404857057903</v>
+        <v>14.73889817310458</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.3798836946501958</v>
+        <v>1.038930717290511</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>3.664839287108798</v>
+        <v>3.20194330264459</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6934</v>
+        <v>7792</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>606.8072647015887</v>
+        <v>607.5373069701751</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>308</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>58.24886973338745</v>
+        <v>70.72581604299671</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>14.16416244791408</v>
+        <v>49.69404857057903</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.7688695124536081</v>
+        <v>0.3798836946501958</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3599938144158952</v>
+        <v>3.664839287108798</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7788</v>
+        <v>6934</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>602.2475004730971</v>
+        <v>606.8072647015887</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>316</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>67.00915609287364</v>
+        <v>58.24886973338745</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>32.69669820477068</v>
+        <v>14.16416244791408</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.6568802807420198</v>
+        <v>0.7688695124536081</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>6.210991171274703</v>
+        <v>0.3599938144158952</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>7795</v>
+        <v>7788</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>586.8236195473513</v>
+        <v>602.2475004730971</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>515</v>
+        <v>316</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>50.31562318544302</v>
+        <v>67.00915609287364</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>22.1605363562161</v>
+        <v>32.69669820477068</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.5546245886807968</v>
+        <v>0.6568802807420198</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-4.104890084246343</v>
+        <v>6.210991171274703</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8040</v>
+        <v>7795</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>571.9774092729659</v>
+        <v>586.8236195473513</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>515</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>62.71629301880729</v>
+        <v>50.31562318544302</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>19.67186384876146</v>
+        <v>22.1605363562161</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.114620571242232</v>
+        <v>0.5546245886807968</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.522028420726464</v>
+        <v>-4.104890084246343</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6918</v>
+        <v>8040</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>569.6389895284323</v>
+        <v>571.9774092729659</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>76.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>58.00706023783115</v>
+        <v>62.71629301880729</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>37.71473788941987</v>
+        <v>19.67186384876146</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5885711258777068</v>
+        <v>2.114620571242232</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.3234609044624276</v>
+        <v>1.522028420726464</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6887</v>
+        <v>6918</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>556.8725907347679</v>
+        <v>569.6389895284323</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>37.6</v>
+        <v>76.2</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>52.3611628064005</v>
+        <v>58.00706023783115</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>27.07454833523722</v>
+        <v>37.71473788941987</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.3572403691824043</v>
+        <v>0.5885711258777068</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0502047953547999</v>
+        <v>0.3234609044624276</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6936</v>
+        <v>6887</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>547.231332071672</v>
+        <v>556.8725907347679</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>32.8</v>
+        <v>37.6</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>56.85879771874646</v>
+        <v>52.3611628064005</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>34.19071062153127</v>
+        <v>27.07454833523722</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4358842950569969</v>
+        <v>0.3572403691824043</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0520912139311051</v>
+        <v>0.0502047953547999</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8039</v>
+        <v>6936</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>517.0379584725647</v>
+        <v>547.231332071672</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>313.5</v>
+        <v>32.8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>61.90696695695472</v>
+        <v>56.85879771874646</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>38.59735002939057</v>
+        <v>34.19071062153127</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.603795847256466</v>
+        <v>0.4358842950569969</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>2.21360307768094</v>
+        <v>0.0520912139311051</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6855</v>
+        <v>8039</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>516.7248614847003</v>
+        <v>517.0379584725647</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>117</v>
+        <v>313.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>52.36791131339754</v>
+        <v>61.90696695695472</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10.63565688654636</v>
+        <v>38.59735002939057</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.2863852692395618</v>
+        <v>0.603795847256466</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>1.597614958756845</v>
+        <v>2.21360307768094</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7810</v>
+        <v>6855</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>505.0776157896217</v>
+        <v>516.7248614847003</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>222</v>
+        <v>117</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>66.18571633251661</v>
+        <v>52.36791131339754</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>34.68909837579702</v>
+        <v>10.63565688654636</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.8505067111476452</v>
+        <v>0.2863852692395618</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>2.363248794329659</v>
+        <v>1.597614958756845</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>7714</v>
+        <v>7810</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>504.6741966444713</v>
+        <v>505.0776157896217</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>168</v>
+        <v>222</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>50.84814651755107</v>
+        <v>66.18571633251661</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>24.46567985633138</v>
+        <v>34.68909837579702</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4404444111720492</v>
+        <v>0.8505067111476452</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.505389071404494</v>
+        <v>2.363248794329659</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6969</v>
+        <v>7714</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>504.0912969713274</v>
+        <v>504.6741966444713</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>34.4</v>
+        <v>168</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>54.6881421521112</v>
+        <v>50.84814651755107</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>22.19023610751866</v>
+        <v>24.46567985633138</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.8770571392659975</v>
+        <v>0.4404444111720492</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.1362965106381006</v>
+        <v>-0.505389071404494</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8034</v>
+        <v>6969</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>477.4641356609457</v>
+        <v>504.0912969713274</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>19.85</v>
+        <v>34.4</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.84951704371872</v>
+        <v>54.6881421521112</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>29.7778847450828</v>
+        <v>22.19023610751866</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.2659063751748364</v>
+        <v>0.8770571392659975</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.2316047874539792</v>
+        <v>-0.1362965106381006</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8021</v>
+        <v>8034</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>477.4536282399807</v>
+        <v>477.4641356609457</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>459</v>
+        <v>19.85</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>57.74399132925908</v>
+        <v>55.84951704371872</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>12.40683156050414</v>
+        <v>29.7778847450828</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.247433542533348</v>
+        <v>0.2659063751748364</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>7.691566292245044</v>
+        <v>0.2316047874539792</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7402</v>
+        <v>8021</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>450.6365264774955</v>
+        <v>477.4536282399807</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>107.5</v>
+        <v>459</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>47.67819271738049</v>
+        <v>57.74399132925908</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>21.14069977332884</v>
+        <v>12.40683156050414</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.2900778385948206</v>
+        <v>1.247433542533348</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.2275254680413113</v>
+        <v>7.691566292245044</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7780</v>
+        <v>7402</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>449.3813482790972</v>
+        <v>450.6365264774955</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>17.05</v>
+        <v>107.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>52.02904536130007</v>
+        <v>47.67819271738049</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>19.05191018925958</v>
+        <v>21.14069977332884</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.517410446753686</v>
+        <v>0.2900778385948206</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0582701483790714</v>
+        <v>0.2275254680413113</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7631</v>
+        <v>7780</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>447.7359369453316</v>
+        <v>449.3813482790972</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>144.5</v>
+        <v>17.05</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>52.51698698083</v>
+        <v>52.02904536130007</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>24.80871889103373</v>
+        <v>19.05191018925958</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5586239561989575</v>
+        <v>1.517410446753686</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.058341725974927</v>
+        <v>0.0582701483790714</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7751</v>
+        <v>7631</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>441.1158056848733</v>
+        <v>447.7359369453316</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1555</v>
+        <v>144.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>50.59920732139</v>
+        <v>52.51698698083</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>19.60893920944804</v>
+        <v>24.80871889103373</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7322753053655185</v>
+        <v>0.5586239561989575</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-2.028962097866327</v>
+        <v>0.058341725974927</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6996</v>
+        <v>7751</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>439.1660160181453</v>
+        <v>441.1158056848733</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>182.5</v>
+        <v>1555</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>54.31857440812751</v>
+        <v>50.59920732139</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>12.21079176385418</v>
+        <v>19.60893920944804</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.9529794060135937</v>
+        <v>0.7322753053655185</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.6501036416440054</v>
+        <v>-2.028962097866327</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7712</v>
+        <v>6996</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>436.6414689971601</v>
+        <v>439.1660160181453</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>152.5</v>
+        <v>182.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>52.06622551395705</v>
+        <v>54.31857440812751</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18.37818002672263</v>
+        <v>12.21079176385418</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3069160188525169</v>
+        <v>0.9529794060135937</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1.703753925387089</v>
+        <v>0.6501036416440054</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6924</v>
+        <v>7712</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>433.8802627161297</v>
+        <v>436.6414689971601</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>113.5</v>
+        <v>152.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.78608383905719</v>
+        <v>52.06622551395705</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>18.21333131383585</v>
+        <v>18.37818002672263</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.1131200925322356</v>
+        <v>0.3069160188525169</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1440769008426427</v>
+        <v>1.703753925387089</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6953</v>
+        <v>6924</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>427.7900161280467</v>
+        <v>433.8802627161297</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>241.5</v>
+        <v>113.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>58.89480204746445</v>
+        <v>49.78608383905719</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>19.46336451057584</v>
+        <v>18.21333131383585</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.147298692701795</v>
+        <v>0.1131200925322356</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>2.084272174109122</v>
+        <v>0.1440769008426427</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7750</v>
+        <v>6953</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>425.8748983265202</v>
+        <v>427.7900161280467</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2300</v>
+        <v>241.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>50.27301621341239</v>
+        <v>58.89480204746445</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>13.22393322106328</v>
+        <v>19.46336451057584</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.4542667584501662</v>
+        <v>1.147298692701795</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-16.8472719306075</v>
+        <v>2.084272174109122</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6951</v>
+        <v>7750</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>420.0420748009792</v>
+        <v>425.8748983265202</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>71.7</v>
+        <v>2300</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>45.17867863945077</v>
+        <v>50.27301621341239</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>23.80743086113249</v>
+        <v>13.22393322106328</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.7692712167420339</v>
+        <v>0.4542667584501662</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.1683200918941731</v>
+        <v>-16.8472719306075</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6994</v>
+        <v>6951</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>410.4936222837678</v>
+        <v>420.0420748009792</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>36.1</v>
+        <v>71.7</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>42.50212158583285</v>
+        <v>45.17867863945077</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>28.53358947553452</v>
+        <v>23.80743086113249</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.216644123654678</v>
+        <v>0.7692712167420339</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.3950129732260921</v>
+        <v>0.1683200918941731</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7805</v>
+        <v>6994</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>401.8136974151348</v>
+        <v>410.4936222837678</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>523</v>
+        <v>36.1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>31.87945455801168</v>
+        <v>42.50212158583285</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>37.21664712120825</v>
+        <v>28.53358947553452</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5775225883720521</v>
+        <v>1.216644123654678</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-13.95642978347236</v>
+        <v>0.3950129732260921</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6952</v>
+        <v>7805</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>399.2068348342306</v>
+        <v>401.8136974151348</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>37</v>
+        <v>523</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>48.2161671246392</v>
+        <v>31.87945455801168</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>17.13773834248957</v>
+        <v>37.21664712120825</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.0569641632460872</v>
+        <v>0.5775225883720521</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.0717933452019993</v>
+        <v>-13.95642978347236</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7689</v>
+        <v>6952</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>390.8211473181461</v>
+        <v>399.2068348342306</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>173</v>
+        <v>37</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>36.48367422461099</v>
+        <v>48.2161671246392</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21.43232746105986</v>
+        <v>17.13773834248957</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.1763208892007137</v>
+        <v>0.0569641632460872</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>2.072691015586691</v>
+        <v>-0.0717933452019993</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6914</v>
+        <v>7689</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>390.8085920320582</v>
+        <v>390.8211473181461</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>122</v>
+        <v>173</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>20.73961389986965</v>
+        <v>36.48367422461099</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>30.14091513173462</v>
+        <v>21.43232746105986</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.3510487221846248</v>
+        <v>0.1763208892007137</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-2.914933655703976</v>
+        <v>2.072691015586691</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6865</v>
+        <v>6914</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>389.2610600530934</v>
+        <v>390.8085920320582</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>25.15</v>
+        <v>122</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.70268996646762</v>
+        <v>20.73961389986965</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>10.62100330198444</v>
+        <v>30.14091513173462</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.60068596023224</v>
+        <v>0.3510487221846248</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.9445111039667092</v>
+        <v>-2.914933655703976</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6931</v>
+        <v>6865</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>387.8582486647418</v>
+        <v>389.2610600530934</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>41.2</v>
+        <v>25.15</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>54.37593951909883</v>
+        <v>52.70268996646762</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>27.91207496970233</v>
+        <v>10.62100330198444</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.322464013632101</v>
+        <v>1.60068596023224</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0236429348639307</v>
+        <v>0.9445111039667092</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7842</v>
+        <v>6931</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>384.7083812879174</v>
+        <v>387.8582486647418</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>41.2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>53.01904179274065</v>
+        <v>54.37593951909883</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>17.15376973695078</v>
+        <v>27.91207496970233</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.3347350646773824</v>
+        <v>0.322464013632101</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.1641934394144009</v>
+        <v>-0.0236429348639307</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6906</v>
+        <v>7842</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>378.2255410260178</v>
+        <v>384.7083812879174</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>53.35413968952131</v>
+        <v>53.01904179274065</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>24.3104596032534</v>
+        <v>17.15376973695078</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.2808392783402395</v>
+        <v>0.3347350646773824</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.900825547762694</v>
+        <v>0.1641934394144009</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6962</v>
+        <v>6906</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>374.9936079151723</v>
+        <v>378.2255410260178</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>32.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>51.46625292543489</v>
+        <v>53.35413968952131</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>17.46220895511985</v>
+        <v>24.3104596032534</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8037879485140483</v>
+        <v>0.2808392783402395</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.2403267829368056</v>
+        <v>0.900825547762694</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>7768</v>
+        <v>6962</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>374.6399577651233</v>
+        <v>374.9936079151723</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>286</v>
+        <v>32.3</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>49.29215234998691</v>
+        <v>51.46625292543489</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>23.01911159357864</v>
+        <v>17.46220895511985</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6418151234051762</v>
+        <v>0.8037879485140483</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>2.962483645467925</v>
+        <v>0.2403267829368056</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>7822</v>
+        <v>7768</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>365.1928736751662</v>
+        <v>374.6399577651233</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>930</v>
+        <v>286</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>52.60165606545103</v>
+        <v>49.29215234998691</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12.28344782266762</v>
+        <v>23.01911159357864</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4793160948181418</v>
+        <v>0.6418151234051762</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>8.316944951498128</v>
+        <v>2.962483645467925</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7730</v>
+        <v>7822</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>363.427971238029</v>
+        <v>365.1928736751662</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>171</v>
+        <v>930</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.65288606743417</v>
+        <v>52.60165606545103</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>14.8676907407798</v>
+        <v>12.28344782266762</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.2789836144897654</v>
+        <v>0.4793160948181418</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.8088044677060315</v>
+        <v>8.316944951498128</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6861</v>
+        <v>7730</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>354.0852076521563</v>
+        <v>363.427971238029</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>190.5</v>
+        <v>171</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>39.24973940440678</v>
+        <v>50.65288606743417</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>23.0633072719362</v>
+        <v>14.8676907407798</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5231623829882077</v>
+        <v>0.2789836144897654</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>2.146423157160024</v>
+        <v>0.8088044677060315</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8028</v>
+        <v>6861</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>353.9659281400413</v>
+        <v>354.0852076521563</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>245.5</v>
+        <v>190.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>43.00476414126144</v>
+        <v>39.24973940440678</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>21.10768272442903</v>
+        <v>23.0633072719362</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8407432513454547</v>
+        <v>0.5231623829882077</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>1.428955846688348</v>
+        <v>2.146423157160024</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3495,21 +3495,21 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7703</v>
+        <v>8028</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>349.7875546613541</v>
+        <v>353.9659281400413</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>179</v>
+        <v>245.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>48.17016024820192</v>
+        <v>43.00476414126144</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>8.967410419143953</v>
+        <v>21.10768272442903</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.9846178042696312</v>
+        <v>0.8407432513454547</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.7653001721152639</v>
+        <v>1.428955846688348</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6903</v>
+        <v>7703</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>346.8996504052841</v>
+        <v>349.7875546613541</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>310</v>
+        <v>179</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>43.18082998291255</v>
+        <v>48.17016024820192</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>14.76160087006752</v>
+        <v>8.967410419143953</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6594025369388516</v>
+        <v>0.9846178042696312</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>2.147750220224697</v>
+        <v>0.7653001721152639</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6895</v>
+        <v>6903</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>344.9702401872839</v>
+        <v>346.8996504052841</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>161.5</v>
+        <v>310</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>72.80732897492837</v>
+        <v>43.18082998291255</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>30.47810508991356</v>
+        <v>14.76160087006752</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.317354113599789</v>
+        <v>0.6594025369388516</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>4.972108725699624</v>
+        <v>2.147750220224697</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6967</v>
+        <v>6895</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>337.3400802599048</v>
+        <v>344.9702401872839</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>72</v>
+        <v>161.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>49.42641151588038</v>
+        <v>72.80732897492837</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>7.491698921533544</v>
+        <v>30.47810508991356</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.3423797326070274</v>
+        <v>1.317354113599789</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0189923731918274</v>
+        <v>4.972108725699624</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8011</v>
+        <v>6967</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>336.8310791245363</v>
+        <v>337.3400802599048</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45.02038606512752</v>
+        <v>49.42641151588038</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>28.22073088314417</v>
+        <v>7.491698921533544</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5705274091866812</v>
+        <v>0.3423797326070274</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0362151090619479</v>
+        <v>0.0189923731918274</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6944</v>
+        <v>8011</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>325.6539264573948</v>
+        <v>336.8310791245363</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>709</v>
+        <v>16</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>38.32531896887576</v>
+        <v>45.02038606512752</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>26.29742305735062</v>
+        <v>28.22073088314417</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.414976319922858</v>
+        <v>0.5705274091866812</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>5.888064057729459</v>
+        <v>0.0362151090619479</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7818</v>
+        <v>6944</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>311.9481309832167</v>
+        <v>325.6539264573948</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>60.6</v>
+        <v>709</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>32.64285691447766</v>
+        <v>38.32531896887576</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20.79205555897209</v>
+        <v>26.29742305735062</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.8164395966595468</v>
+        <v>1.414976319922858</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0177099839574772</v>
+        <v>5.888064057729459</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6997</v>
+        <v>7818</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>311.1064948309637</v>
+        <v>311.9481309832167</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>68</v>
+        <v>60.6</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>52.26044000710795</v>
+        <v>32.64285691447766</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>7.828400981533369</v>
+        <v>20.79205555897209</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.3976712372347533</v>
+        <v>0.8164395966595468</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>1.962392430755349</v>
+        <v>-0.0177099839574772</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>7760</v>
+        <v>6997</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>310.8530918149116</v>
+        <v>311.1064948309637</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>33.2</v>
+        <v>68</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>48.27195096577679</v>
+        <v>52.26044000710795</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>7.683206632709654</v>
+        <v>7.828400981533369</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4057265881503719</v>
+        <v>0.3976712372347533</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0461055181253428</v>
+        <v>1.962392430755349</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>7839</v>
+        <v>7760</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>310.2290986442731</v>
+        <v>310.8530918149116</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>44.2</v>
+        <v>33.2</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>40.33793899666905</v>
+        <v>48.27195096577679</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>32.38963158388495</v>
+        <v>7.683206632709654</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.1657078625618988</v>
+        <v>0.4057265881503719</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0541734276592485</v>
+        <v>0.0461055181253428</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7721</v>
+        <v>7839</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>308.6140940157317</v>
+        <v>310.2290986442731</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>61.3</v>
+        <v>44.2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>43.98372518940944</v>
+        <v>40.33793899666905</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16.35923929432947</v>
+        <v>32.38963158388495</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7891323309389536</v>
+        <v>0.1657078625618988</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.1990701610812386</v>
+        <v>-0.0541734276592485</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6957</v>
+        <v>7721</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>307.7497825415425</v>
+        <v>308.6140940157317</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>218</v>
+        <v>61.3</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>49.69590638421868</v>
+        <v>43.98372518940944</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>14.30406678530393</v>
+        <v>16.35923929432947</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6412116012802322</v>
+        <v>0.7891323309389536</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.191550823788254</v>
+        <v>0.1990701610812386</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7717</v>
+        <v>6957</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>307.250836952789</v>
+        <v>307.7497825415425</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>423</v>
+        <v>218</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.56730202503893</v>
+        <v>49.69590638421868</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>14.00046563261259</v>
+        <v>14.30406678530393</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6051894429811101</v>
+        <v>0.6412116012802322</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>4.680927775421932</v>
+        <v>0.191550823788254</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>7769</v>
+        <v>7717</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>304.3564568648052</v>
+        <v>307.250836952789</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>5710</v>
+        <v>423</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>37.76117872294108</v>
+        <v>49.56730202503893</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10.15577287155746</v>
+        <v>14.00046563261259</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.446283910565189</v>
+        <v>0.6051894429811101</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-71.61301638495775</v>
+        <v>4.680927775421932</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8033</v>
+        <v>7769</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>299.9079035090236</v>
+        <v>304.3564568648052</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>181</v>
+        <v>5710</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>47.25274898826962</v>
+        <v>37.76117872294108</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13.6280366326588</v>
+        <v>10.15577287155746</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4856086091883982</v>
+        <v>1.446283910565189</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.3322130488850846</v>
+        <v>-71.61301638495775</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6910</v>
+        <v>8033</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>298.196546869164</v>
+        <v>299.9079035090236</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>25.3</v>
+        <v>181</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>56.22194935196696</v>
+        <v>47.25274898826962</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19.10277803040715</v>
+        <v>13.6280366326588</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.018656993455734</v>
+        <v>0.4856086091883982</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.1479092137469211</v>
+        <v>-0.3322130488850846</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>7855</v>
+        <v>6910</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>296.6652682367731</v>
+        <v>298.196546869164</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>42.75</v>
+        <v>25.3</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>17.66986279692568</v>
+        <v>56.22194935196696</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>48.9471121702631</v>
+        <v>19.10277803040715</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4662923122679228</v>
+        <v>1.018656993455734</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1.273167975092308</v>
+        <v>0.1479092137469211</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6928</v>
+        <v>7855</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>295.6355136158841</v>
+        <v>296.6652682367731</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>48.4</v>
+        <v>42.75</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>48.960928835476</v>
+        <v>17.66986279692568</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>12.94398929522672</v>
+        <v>48.9471121702631</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.3600213521396665</v>
+        <v>0.4662923122679228</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1056019093852161</v>
+        <v>1.273167975092308</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6965</v>
+        <v>6928</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>295.102320236802</v>
+        <v>295.6355136158841</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>73.40000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>36.41728617745388</v>
+        <v>48.960928835476</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>36.51748315444473</v>
+        <v>12.94398929522672</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.729427037587671</v>
+        <v>0.3600213521396665</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0192640038450404</v>
+        <v>0.1056019093852161</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8042</v>
+        <v>6965</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>294.9394804199615</v>
+        <v>295.102320236802</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>111</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>49.19517343641551</v>
+        <v>36.41728617745388</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.87337683063816</v>
+        <v>36.51748315444473</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.8691643293477794</v>
+        <v>1.729427037587671</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>2.14484185038956</v>
+        <v>-0.0192640038450404</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6983</v>
+        <v>8042</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>286.6478892328631</v>
+        <v>294.9394804199615</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>345.5</v>
+        <v>111</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>60.71730193062274</v>
+        <v>49.19517343641551</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19.00356548003512</v>
+        <v>18.87337683063816</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.7946726070573737</v>
+        <v>0.8691643293477794</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>7.797559087791106</v>
+        <v>2.14484185038956</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6916</v>
+        <v>6983</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>280.0273591508665</v>
+        <v>286.6478892328631</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>18.5</v>
+        <v>345.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>47.1109755334784</v>
+        <v>60.71730193062274</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>9.07854051933254</v>
+        <v>19.00356548003512</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6920552062324515</v>
+        <v>0.7946726070573737</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0249951638763285</v>
+        <v>7.797559087791106</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6901</v>
+        <v>6916</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>274.4331965512545</v>
+        <v>280.0273591508665</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>15.25</v>
+        <v>18.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>38.28360834069138</v>
+        <v>47.1109755334784</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>11.08896414995865</v>
+        <v>9.07854051933254</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.3927219977392818</v>
+        <v>0.6920552062324515</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.1345258278337238</v>
+        <v>0.0249951638763285</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7610</v>
+        <v>6901</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>269.1449620923295</v>
+        <v>274.4331965512545</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1520</v>
+        <v>15.25</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>43.07862612291101</v>
+        <v>38.28360834069138</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.02895847259269</v>
+        <v>11.08896414995865</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.8283324735702843</v>
+        <v>0.3927219977392818</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-6.703801596759945</v>
+        <v>-0.1345258278337238</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7734</v>
+        <v>7610</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>268.6825773063284</v>
+        <v>269.1449620923295</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>2795</v>
+        <v>1520</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>42.4529328400646</v>
+        <v>43.07862612291101</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16.0768697851357</v>
+        <v>13.02895847259269</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.3925757794760908</v>
+        <v>0.8283324735702843</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-19.60257584892571</v>
+        <v>-6.703801596759945</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8016</v>
+        <v>7734</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>267.6799533701939</v>
+        <v>268.6825773063284</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>295</v>
+        <v>2795</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>48.92708098824394</v>
+        <v>42.4529328400646</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>9.658089629310432</v>
+        <v>16.0768697851357</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3763192012782784</v>
+        <v>0.3925757794760908</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.1663278054837845</v>
+        <v>-19.60257584892571</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6971</v>
+        <v>8016</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>265.0018594863294</v>
+        <v>267.6799533701939</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>26</v>
+        <v>295</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>46.27424167514548</v>
+        <v>48.92708098824394</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16.4905802325531</v>
+        <v>9.658089629310432</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5898364564821272</v>
+        <v>0.3763192012782784</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.07515872218127501</v>
+        <v>-0.1663278054837845</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7799</v>
+        <v>6971</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>261.8589732218762</v>
+        <v>265.0018594863294</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>360</v>
+        <v>26</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46.71105997612174</v>
+        <v>46.27424167514548</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>14.95445585522914</v>
+        <v>16.4905802325531</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.9681858795772912</v>
+        <v>0.5898364564821272</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>1.943041590770205</v>
+        <v>0.07515872218127501</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6877</v>
+        <v>7799</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>254.2054067394993</v>
+        <v>261.8589732218762</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>113.5</v>
+        <v>360</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>40.72840320097676</v>
+        <v>46.71105997612174</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>21.02301250102793</v>
+        <v>14.95445585522914</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.8808222983609594</v>
+        <v>0.9681858795772912</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.2390320159049856</v>
+        <v>1.943041590770205</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6899</v>
+        <v>6877</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>252.934406067484</v>
+        <v>254.2054067394993</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>49.85</v>
+        <v>113.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>38.2351627258221</v>
+        <v>40.72840320097676</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>20.31218542106153</v>
+        <v>21.02301250102793</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3298221022036239</v>
+        <v>0.8808222983609594</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>2</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1606395682906307</v>
+        <v>-0.2390320159049856</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8032</v>
+        <v>6899</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>238.1432366099819</v>
+        <v>252.934406067484</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>35.95</v>
+        <v>49.85</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>43.22817565145502</v>
+        <v>38.2351627258221</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19.23086463794662</v>
+        <v>20.31218542106153</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.584178739700369</v>
+        <v>0.3298221022036239</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>2</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1698162004494188</v>
+        <v>0.1606395682906307</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7791</v>
+        <v>8032</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>236.5370136552024</v>
+        <v>238.1432366099819</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>55.9</v>
+        <v>35.95</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>25.28801202726994</v>
+        <v>43.22817565145502</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>37.7985473847828</v>
+        <v>19.23086463794662</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6213635251911395</v>
+        <v>1.584178739700369</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0346108597815362</v>
+        <v>0.1698162004494188</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6923</v>
+        <v>7791</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>231.0154163752496</v>
+        <v>236.5370136552024</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>55.9</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>44.81858135699966</v>
+        <v>25.28801202726994</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>7.854842853812198</v>
+        <v>37.7985473847828</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.550291339285877</v>
+        <v>0.6213635251911395</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.025372832526636</v>
+        <v>0.0346108597815362</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>7736</v>
+        <v>6923</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>228.2473440722527</v>
+        <v>231.0154163752496</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>69.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45.00800697308206</v>
+        <v>44.81858135699966</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.88492080668972</v>
+        <v>7.854842853812198</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.2839538792788437</v>
+        <v>0.550291339285877</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0484342470126484</v>
+        <v>-0.025372832526636</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6902</v>
+        <v>7736</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>227.7589583809392</v>
+        <v>228.2473440722527</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>124</v>
+        <v>69.2</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>44.60555595005022</v>
+        <v>45.00800697308206</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.31786792439301</v>
+        <v>14.88492080668972</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.305336295343265</v>
+        <v>0.2839538792788437</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.2940796079859422</v>
+        <v>-0.0484342470126484</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6862</v>
+        <v>6902</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>225.7986371905462</v>
+        <v>227.7589583809392</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>139.5</v>
+        <v>124</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>44.21746883155377</v>
+        <v>44.60555595005022</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>14.51700064236035</v>
+        <v>12.31786792439301</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.403746397066673</v>
+        <v>1.305336295343265</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>1.308141697723278</v>
+        <v>-0.2940796079859422</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7770</v>
+        <v>6862</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>225.7884797610291</v>
+        <v>225.7986371905462</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>35.85</v>
+        <v>139.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>48.73848696892134</v>
+        <v>44.21746883155377</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>5.555531824694961</v>
+        <v>14.51700064236035</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>2.434178544001916</v>
+        <v>0.403746397066673</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0356080565073333</v>
+        <v>1.308141697723278</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6955</v>
+        <v>7770</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>225.2743390078552</v>
+        <v>225.7884797610291</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>103</v>
+        <v>35.85</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>47.43710198311041</v>
+        <v>48.73848696892134</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>6.502264778204085</v>
+        <v>5.555531824694961</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.015228426395939</v>
+        <v>2.434178544001916</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-1.016830558887249</v>
+        <v>-0.0356080565073333</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6908</v>
+        <v>6955</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>223.8725433494699</v>
+        <v>225.2743390078552</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>30.3</v>
+        <v>103</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>33.23976335067067</v>
+        <v>47.43710198311041</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>34.66929814547262</v>
+        <v>6.502264778204085</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.8303569320638517</v>
+        <v>1.015228426395939</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.051295324355058</v>
+        <v>-1.016830558887249</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7704</v>
+        <v>6908</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>223.7644627593105</v>
+        <v>223.8725433494699</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>61.6</v>
+        <v>30.3</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.2082282389915</v>
+        <v>33.23976335067067</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>17.11857074272752</v>
+        <v>34.66929814547262</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.6111592288606484</v>
+        <v>0.8303569320638517</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.3049440645039081</v>
+        <v>0.051295324355058</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7765</v>
+        <v>7704</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>222.3083659788143</v>
+        <v>223.7644627593105</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>223.5</v>
+        <v>61.6</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>46.18532188970868</v>
+        <v>50.2082282389915</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>24.16212836029131</v>
+        <v>17.11857074272752</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.2399927343732261</v>
+        <v>0.6111592288606484</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.037626733028633</v>
+        <v>-0.3049440645039081</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>7749</v>
+        <v>7765</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>218.2586678834756</v>
+        <v>222.3083659788143</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>370</v>
+        <v>223.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>52.8633311117805</v>
+        <v>46.18532188970868</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>18.7391680627671</v>
+        <v>24.16212836029131</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.233551551128256</v>
+        <v>0.2399927343732261</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>4.251555596520998</v>
+        <v>0.037626733028633</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>7820</v>
+        <v>7749</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>216.6240186531407</v>
+        <v>218.2586678834756</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>119.5</v>
+        <v>370</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>53.90328488769854</v>
+        <v>52.8633311117805</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18.65189261791906</v>
+        <v>18.7391680627671</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.2024492311841161</v>
+        <v>1.233551551128256</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0015362860590069</v>
+        <v>4.251555596520998</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6863</v>
+        <v>7820</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>212.0324712700686</v>
+        <v>216.6240186531407</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>107</v>
+        <v>119.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>40.15702166591772</v>
+        <v>53.90328488769854</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.72170544006039</v>
+        <v>18.65189261791906</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.3602651002813619</v>
+        <v>0.2024492311841161</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-1.127937363518141</v>
+        <v>0.0015362860590069</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>7828</v>
+        <v>6863</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>211.6871379555474</v>
+        <v>212.0324712700686</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>1760</v>
+        <v>107</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,49 +5852,49 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>53.20315576189849</v>
+        <v>40.15702166591772</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>12.78711204090184</v>
+        <v>16.72170544006039</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.7342740005082912</v>
+        <v>0.3602651002813619</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>24.94492867253227</v>
+        <v>-1.127937363518141</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7821</v>
+        <v>7828</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>211.6691689474428</v>
+        <v>211.6871379555474</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>39.7</v>
+        <v>1760</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,49 +5905,49 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>49.67656893749707</v>
+        <v>53.20315576189849</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>12.5583337552479</v>
+        <v>12.78711204090184</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6697613555162711</v>
+        <v>0.7342740005082912</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.1168775844808667</v>
+        <v>24.94492867253227</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7823</v>
+        <v>7821</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>204.2651430374766</v>
+        <v>211.6691689474428</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>39.7</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>50.6044579458053</v>
+        <v>49.67656893749707</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>22.08552634900181</v>
+        <v>12.5583337552479</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3738682905798663</v>
+        <v>0.6697613555162711</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0456492121607856</v>
+        <v>0.1168775844808667</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8024</v>
+        <v>7823</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>196.3200661834283</v>
+        <v>204.2651430374766</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>13</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>36.22804945692324</v>
+        <v>50.6044579458053</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.68077924026136</v>
+        <v>22.08552634900181</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.7086621082121123</v>
+        <v>0.3738682905798663</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0144507389758308</v>
+        <v>-0.0456492121607856</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>7705</v>
+        <v>8024</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>193.682154913081</v>
+        <v>196.3200661834283</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>30.15</v>
+        <v>13</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>43.19712061478051</v>
+        <v>36.22804945692324</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.22088303822173</v>
+        <v>13.68077924026136</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.767309907314597</v>
+        <v>0.7086621082121123</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0512895326190626</v>
+        <v>0.0144507389758308</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6890</v>
+        <v>7705</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>192.8338976279259</v>
+        <v>193.682154913081</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>166.5</v>
+        <v>30.15</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45.80571872010565</v>
+        <v>43.19712061478051</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.42980196346315</v>
+        <v>18.22088303822173</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4799887205526187</v>
+        <v>1.767309907314597</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>1.228577500579307</v>
+        <v>-0.0512895326190626</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>7827</v>
+        <v>6890</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>191.0829019299831</v>
+        <v>192.8338976279259</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>152</v>
+        <v>166.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>43.24247654493513</v>
+        <v>45.80571872010565</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>9.861974054800555</v>
+        <v>13.42980196346315</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3108961245254183</v>
+        <v>0.4799887205526187</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.6624857279939108</v>
+        <v>1.228577500579307</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6873</v>
+        <v>7827</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>188.3688606676868</v>
+        <v>191.0829019299831</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>68.90000000000001</v>
+        <v>152</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>36.75016206438912</v>
+        <v>43.24247654493513</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>24.1784038321015</v>
+        <v>9.861974054800555</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5127499396378905</v>
+        <v>0.3108961245254183</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.3699630455957838</v>
+        <v>-0.6624857279939108</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6958</v>
+        <v>6873</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>185.5857248905114</v>
+        <v>188.3688606676868</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>17.1</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>41.8150582936369</v>
+        <v>36.75016206438912</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>15.77784452636157</v>
+        <v>24.1784038321015</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4288584217389772</v>
+        <v>0.5127499396378905</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0665197600853729</v>
+        <v>0.3699630455957838</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8038</v>
+        <v>6958</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>185.0128221852848</v>
+        <v>185.5857248905114</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>31.6</v>
+        <v>17.1</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>42.69233896008268</v>
+        <v>41.8150582936369</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>20.80935687587988</v>
+        <v>15.77784452636157</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6468539186631557</v>
+        <v>0.4288584217389772</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.3618841507066286</v>
+        <v>-0.0665197600853729</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6869</v>
+        <v>8038</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>177.0023889802759</v>
+        <v>185.0128221852848</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>66.59999999999999</v>
+        <v>31.6</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46.66102672760362</v>
+        <v>42.69233896008268</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>15.66627669992302</v>
+        <v>20.80935687587988</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5820836839495062</v>
+        <v>0.6468539186631557</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.2270293522274937</v>
+        <v>0.3618841507066286</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>7732</v>
+        <v>6869</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>169.3897770170266</v>
+        <v>177.0023889802759</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>33.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46.32681655691973</v>
+        <v>46.66102672760362</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>5.375663070124831</v>
+        <v>15.66627669992302</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.0999730072880322</v>
+        <v>0.5820836839495062</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0971910452790026</v>
+        <v>0.2270293522274937</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>7722</v>
+        <v>7732</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>166.2207877259469</v>
+        <v>169.3897770170266</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>277</v>
+        <v>33.8</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>43.96422240925061</v>
+        <v>46.32681655691973</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>11.456382953674</v>
+        <v>5.375663070124831</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5375350382648481</v>
+        <v>0.0999730072880322</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.6572836867931238</v>
+        <v>-0.0971910452790026</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6919</v>
+        <v>7722</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>165.1972409642275</v>
+        <v>166.2207877259469</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>88.09999999999999</v>
+        <v>277</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>32.43732434514739</v>
+        <v>43.96422240925061</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>17.20519020730721</v>
+        <v>11.456382953674</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.9197240964227502</v>
+        <v>0.5375350382648481</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-2.153692307021759</v>
+        <v>0.6572836867931238</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6988</v>
+        <v>6919</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>165.1660669191562</v>
+        <v>165.1972409642275</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>11.3</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>43.49928896935251</v>
+        <v>32.43732434514739</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>6.76883495409595</v>
+        <v>17.20519020730721</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.92282266284674</v>
+        <v>0.9197240964227502</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.040429658120302</v>
+        <v>-2.153692307021759</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6921</v>
+        <v>6988</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>154.3831191840759</v>
+        <v>165.1660669191562</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>63.9</v>
+        <v>11.3</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>43.17392486220163</v>
+        <v>43.49928896935251</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>17.502703884503</v>
+        <v>6.76883495409595</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4579249746535991</v>
+        <v>0.92282266284674</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.5136256282354388</v>
+        <v>-0.040429658120302</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7715</v>
+        <v>6921</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>153.0700654608562</v>
+        <v>154.3831191840759</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>29</v>
+        <v>63.9</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>36.67018472997394</v>
+        <v>43.17392486220163</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>19.71987615570346</v>
+        <v>17.502703884503</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.1456231758796162</v>
+        <v>0.4579249746535991</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.2612016114467367</v>
+        <v>-0.5136256282354388</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6947</v>
+        <v>7715</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>152.9362927368221</v>
+        <v>153.0700654608562</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>29</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>36.06094218943922</v>
+        <v>36.67018472997394</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>12.15270597711375</v>
+        <v>19.71987615570346</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.7719376848503727</v>
+        <v>0.1456231758796162</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.1195331356838744</v>
+        <v>-0.2612016114467367</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>7786</v>
+        <v>6947</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>148.8832657513748</v>
+        <v>152.9362927368221</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>116.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>35.8149214418772</v>
+        <v>36.06094218943922</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>14.57329170803167</v>
+        <v>12.15270597711375</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.4541890343205259</v>
+        <v>0.7719376848503727</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.6797418225318181</v>
+        <v>0.1195331356838744</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>7772</v>
+        <v>7786</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>143.8275933006296</v>
+        <v>148.8832657513748</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>90.5</v>
+        <v>116.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>45.29756273255654</v>
+        <v>35.8149214418772</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>15.00998884253741</v>
+        <v>14.57329170803167</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.054645120215786</v>
+        <v>0.4541890343205259</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>1.327262932849986</v>
+        <v>-0.6797418225318181</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>7803</v>
+        <v>7772</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>140.6450041143216</v>
+        <v>143.8275933006296</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>19.4</v>
+        <v>90.5</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>42.88748577407009</v>
+        <v>45.29756273255654</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>12.32463350008373</v>
+        <v>15.00998884253741</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.4428483219526369</v>
+        <v>1.054645120215786</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0881761706304767</v>
+        <v>1.327262932849986</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>7747</v>
+        <v>7803</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>135.7453656501359</v>
+        <v>140.6450041143216</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>113</v>
+        <v>19.4</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>51.94259230888803</v>
+        <v>42.88748577407009</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>8.346614305821639</v>
+        <v>12.32463350008373</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.1537404580152671</v>
+        <v>0.4428483219526369</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>2.375646822857013</v>
+        <v>0.0881761706304767</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>7740</v>
+        <v>7747</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>131.6050866473846</v>
+        <v>135.7453656501359</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>130.5</v>
+        <v>113</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>37.91993732340356</v>
+        <v>51.94259230888803</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>13.42671189193489</v>
+        <v>8.346614305821639</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.1577527127837088</v>
+        <v>0.1537404580152671</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.9459840650307348</v>
+        <v>2.375646822857013</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>7547</v>
+        <v>7740</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>124.2492308965919</v>
+        <v>131.6050866473846</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>50.8</v>
+        <v>130.5</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>44.78858156173285</v>
+        <v>37.91993732340356</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>12.29681310020194</v>
+        <v>13.42671189193489</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.2595669903467036</v>
+        <v>0.1577527127837088</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0532296027214436</v>
+        <v>-0.9459840650307348</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6925</v>
+        <v>7547</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>114.4853763554116</v>
+        <v>124.2492308965919</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>41.91086029902335</v>
+        <v>44.78858156173285</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>11.66712938744022</v>
+        <v>12.29681310020194</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.5407048600864045</v>
+        <v>0.2595669903467036</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.2103015141128688</v>
+        <v>-0.0532296027214436</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>7753</v>
+        <v>6925</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>99.37674692475488</v>
+        <v>114.4853763554116</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>36.35</v>
+        <v>50.6</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>35.84990012874209</v>
+        <v>41.91086029902335</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>9.22461064705508</v>
+        <v>11.66712938744022</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.489243968170438</v>
+        <v>0.5407048600864045</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.020677508586967</v>
+        <v>0.2103015141128688</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7205,52 +7205,105 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
+        <v>7753</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>星亞</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>99.37674692475488</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>35.84990012874209</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>9.22461064705508</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.489243968170438</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>0.020677508586967</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
         <v>6909</v>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>創控</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D128" s="2" t="n">
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
         <v>89.77156541336858</v>
       </c>
-      <c r="E128" s="2" t="n">
+      <c r="E129" s="2" t="n">
         <v>40.9</v>
       </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H128" s="2" t="n">
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
         <v>45.58349253649961</v>
       </c>
-      <c r="I128" s="2" t="n">
+      <c r="I129" s="2" t="n">
         <v>16.06131901765144</v>
       </c>
-      <c r="J128" s="2" t="n">
+      <c r="J129" s="2" t="n">
         <v>0.7053828007244648</v>
       </c>
-      <c r="K128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N128" s="2" t="n">
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
         <v>0.4140842992026177</v>
       </c>
-      <c r="O128" s="2" t="inlineStr">
+      <c r="O129" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
